--- a/90_temp/01_品目工程・品目構成 - コピー/kensyou/02_購買課確認用_工程不一致分.xlsx
+++ b/90_temp/01_品目工程・品目構成 - コピー/kensyou/02_購買課確認用_工程不一致分.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\fsrv24\TempFile\20250908_購買課依頼内容\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\90_tools\90_temp\01_品目工程・品目構成\kensyou\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9750" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9750"/>
   </bookViews>
   <sheets>
     <sheet name="購買課確認用_工程マスタ不一致" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="160">
   <si>
     <t>区分コード</t>
   </si>
@@ -92,12 +92,6 @@
     <t>伊東</t>
   </si>
   <si>
-    <t>SPL-2721AA</t>
-  </si>
-  <si>
-    <t>165-209BA-TEMP</t>
-  </si>
-  <si>
     <t>横田</t>
   </si>
   <si>
@@ -137,36 +131,6 @@
     <t>VN-SPL-2944-204JA2200</t>
   </si>
   <si>
-    <t>柴田</t>
-  </si>
-  <si>
-    <t>100-226CA</t>
-  </si>
-  <si>
-    <t>SS400-100X400X36.7</t>
-  </si>
-  <si>
-    <t>@</t>
-  </si>
-  <si>
-    <t>KS91-00301CB30</t>
-  </si>
-  <si>
-    <t>S45C-32X120X200</t>
-  </si>
-  <si>
-    <t>KS91-00302BA32</t>
-  </si>
-  <si>
-    <t>S50C-120X200X22</t>
-  </si>
-  <si>
-    <t>KS91-00302BB32</t>
-  </si>
-  <si>
-    <t>KS91-00302BC32</t>
-  </si>
-  <si>
     <t>A</t>
   </si>
   <si>
@@ -260,12 +224,6 @@
     <t>宮木</t>
   </si>
   <si>
-    <t>KS91-00829CA</t>
-  </si>
-  <si>
-    <t>S50C-32X150X300</t>
-  </si>
-  <si>
     <t>YS65-04908BA</t>
   </si>
   <si>
@@ -290,12 +248,6 @@
     <t>FSP-20-001AA</t>
   </si>
   <si>
-    <t>582-503C</t>
-  </si>
-  <si>
-    <t>S50C-6.35X120X390</t>
-  </si>
-  <si>
     <t>G</t>
   </si>
   <si>
@@ -377,12 +329,6 @@
     <t>大澤</t>
   </si>
   <si>
-    <t>K-30404VA34</t>
-  </si>
-  <si>
-    <t>SS400-14X17X68.5</t>
-  </si>
-  <si>
     <t>YD65-151CA</t>
   </si>
   <si>
@@ -422,15 +368,6 @@
     <t>100-105-3-220</t>
   </si>
   <si>
-    <t>Q</t>
-  </si>
-  <si>
-    <t>E-26820EA38</t>
-  </si>
-  <si>
-    <t>S45C-20X130X200</t>
-  </si>
-  <si>
     <t>T</t>
   </si>
   <si>
@@ -446,40 +383,16 @@
     <t>栗山</t>
   </si>
   <si>
-    <t>K-25046FA</t>
-  </si>
-  <si>
-    <t>SS400-14X14X155</t>
-  </si>
-  <si>
     <t>K-25046EA</t>
   </si>
   <si>
     <t>SS400-14X30X52</t>
   </si>
   <si>
-    <t>K-6509DA21</t>
-  </si>
-  <si>
-    <t>S50C-90X40X27</t>
-  </si>
-  <si>
-    <t>K-25058AA</t>
-  </si>
-  <si>
-    <t>SS400-44X92X6</t>
-  </si>
-  <si>
     <t>K-25001UA</t>
   </si>
   <si>
     <t>FSP-21-001AA</t>
-  </si>
-  <si>
-    <t>K-25059AA</t>
-  </si>
-  <si>
-    <t>SS400-100X100X6</t>
   </si>
   <si>
     <t>E-16764E</t>
@@ -2112,7 +2025,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U67"/>
+  <dimension ref="A1:U53"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3.625" style="2" customWidth="1"/>
@@ -2197,14 +2110,14 @@
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="A2" s="2">
-        <v>1</v>
+      <c r="A2" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -2213,13 +2126,16 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I2" t="s">
+        <v>45</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2248,13 +2164,13 @@
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -2263,13 +2179,16 @@
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I3" t="s">
+        <v>40</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2298,13 +2217,13 @@
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -2313,7 +2232,7 @@
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -2348,13 +2267,13 @@
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -2363,7 +2282,7 @@
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -2398,13 +2317,13 @@
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
         <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -2413,7 +2332,7 @@
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -2448,13 +2367,13 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
         <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -2463,31 +2382,43 @@
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I7" t="s">
+        <v>52</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="L7" t="s">
+        <v>53</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O7" t="s">
+        <v>54</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="R7" t="s">
+        <v>55</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -2498,13 +2429,13 @@
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B8" t="s">
         <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -2513,16 +2444,13 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="I8" t="s">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2551,13 +2479,13 @@
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s">
         <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -2566,7 +2494,7 @@
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2601,31 +2529,28 @@
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="B10" t="s">
         <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="I10" t="s">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2654,13 +2579,13 @@
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="B11" t="s">
         <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -2669,7 +2594,7 @@
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2704,13 +2629,13 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -2719,7 +2644,7 @@
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2754,13 +2679,13 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -2769,43 +2694,31 @@
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>1</v>
-      </c>
-      <c r="I13" t="s">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>1</v>
-      </c>
-      <c r="L13" t="s">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="M13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13">
-        <v>1</v>
-      </c>
-      <c r="O13" t="s">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="P13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q13">
-        <v>1</v>
-      </c>
-      <c r="R13" t="s">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -2816,13 +2729,13 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -2831,7 +2744,7 @@
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2866,22 +2779,22 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2916,13 +2829,13 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -2931,7 +2844,7 @@
         <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2966,13 +2879,13 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B17" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -2981,25 +2894,19 @@
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>1</v>
-      </c>
-      <c r="I17" t="s">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="J17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17">
-        <v>1</v>
-      </c>
-      <c r="L17" t="s">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="M17">
         <v>0</v>
@@ -3022,13 +2929,13 @@
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B18" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -3037,19 +2944,25 @@
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I18" t="s">
+        <v>78</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="L18" t="s">
+        <v>79</v>
       </c>
       <c r="M18">
         <v>0</v>
@@ -3072,13 +2985,13 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B19" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="C19" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -3087,7 +3000,7 @@
         <v>1</v>
       </c>
       <c r="F19" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -3122,13 +3035,13 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B20" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -3137,7 +3050,7 @@
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -3171,14 +3084,14 @@
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A21" s="2" t="s">
-        <v>90</v>
+      <c r="A21" s="2">
+        <v>2</v>
       </c>
       <c r="B21" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="C21" t="s">
-        <v>102</v>
+        <v>32</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -3187,13 +3100,16 @@
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>103</v>
+        <v>33</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I21" t="s">
+        <v>34</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -3221,14 +3137,14 @@
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A22" s="2" t="s">
-        <v>90</v>
+      <c r="A22" s="2">
+        <v>2</v>
       </c>
       <c r="B22" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="C22" t="s">
-        <v>104</v>
+        <v>23</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -3237,13 +3153,16 @@
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>105</v>
+        <v>24</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I22" t="s">
+        <v>25</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -3271,14 +3190,14 @@
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A23" s="2" t="s">
-        <v>90</v>
+      <c r="A23" s="2">
+        <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="C23" t="s">
-        <v>106</v>
+        <v>26</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -3287,13 +3206,16 @@
         <v>1</v>
       </c>
       <c r="F23" t="s">
-        <v>107</v>
+        <v>27</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I23" t="s">
+        <v>28</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -3321,14 +3243,14 @@
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A24" s="2" t="s">
-        <v>90</v>
+      <c r="A24" s="2">
+        <v>2</v>
       </c>
       <c r="B24" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>108</v>
+        <v>29</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -3337,13 +3259,16 @@
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>109</v>
+        <v>30</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I24" t="s">
+        <v>31</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -3372,13 +3297,13 @@
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A25" s="2" t="s">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="B25" t="s">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="C25" t="s">
-        <v>110</v>
+        <v>66</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -3387,13 +3312,13 @@
         <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>111</v>
+        <v>67</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -3421,14 +3346,14 @@
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A26" s="2">
-        <v>2</v>
+      <c r="A26" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="B26" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="C26" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -3437,16 +3362,13 @@
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26">
-        <v>1</v>
-      </c>
-      <c r="I26" t="s">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -3474,32 +3396,23 @@
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A27" s="2">
-        <v>2</v>
+      <c r="A27" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="B27" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="C27" t="s">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="D27">
         <v>1</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F27" t="s">
-        <v>29</v>
-      </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
-      <c r="H27">
-        <v>1</v>
-      </c>
-      <c r="I27" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -3527,14 +3440,14 @@
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A28" s="2">
-        <v>2</v>
+      <c r="A28" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="B28" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="C28" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -3543,16 +3456,13 @@
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="G28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28">
-        <v>1</v>
-      </c>
-      <c r="I28" t="s">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -3580,14 +3490,14 @@
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A29" s="2">
-        <v>2</v>
+      <c r="A29" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="B29" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="C29" t="s">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -3596,16 +3506,13 @@
         <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29">
-        <v>1</v>
-      </c>
-      <c r="I29" t="s">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -3634,22 +3541,22 @@
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A30" s="2" t="s">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="B30" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C30" t="s">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="D30">
         <v>1</v>
       </c>
       <c r="E30">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F30" t="s">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -3684,13 +3591,13 @@
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A31" s="2" t="s">
-        <v>76</v>
+        <v>117</v>
       </c>
       <c r="B31" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="C31" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -3699,13 +3606,13 @@
         <v>1</v>
       </c>
       <c r="F31" t="s">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -3734,13 +3641,13 @@
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A32" s="2" t="s">
-        <v>76</v>
+        <v>117</v>
       </c>
       <c r="B32" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="C32" t="s">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -3749,7 +3656,7 @@
         <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -3784,22 +3691,28 @@
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A33" s="2" t="s">
-        <v>76</v>
+        <v>117</v>
       </c>
       <c r="B33" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="C33" t="s">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="D33">
         <v>1</v>
       </c>
       <c r="E33">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F33" t="s">
-        <v>85</v>
+        <v>98</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -3828,13 +3741,13 @@
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A34" s="2" t="s">
-        <v>76</v>
+        <v>117</v>
       </c>
       <c r="B34" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="C34" t="s">
-        <v>86</v>
+        <v>124</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -3843,7 +3756,7 @@
         <v>1</v>
       </c>
       <c r="F34" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -3878,13 +3791,13 @@
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A35" s="2" t="s">
-        <v>76</v>
+        <v>117</v>
       </c>
       <c r="B35" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="C35" t="s">
-        <v>88</v>
+        <v>145</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -3893,7 +3806,7 @@
         <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>89</v>
+        <v>146</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -3928,13 +3841,13 @@
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A36" s="2" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B36" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="C36" t="s">
-        <v>113</v>
+        <v>147</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -3943,7 +3856,7 @@
         <v>1</v>
       </c>
       <c r="F36" t="s">
-        <v>114</v>
+        <v>148</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -3978,22 +3891,22 @@
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A37" s="2" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B37" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="C37" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="D37">
         <v>1</v>
       </c>
       <c r="E37">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F37" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -4028,22 +3941,22 @@
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A38" s="2" t="s">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="B38" t="s">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="C38" t="s">
-        <v>140</v>
+        <v>103</v>
       </c>
       <c r="D38">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F38" t="s">
-        <v>141</v>
+        <v>104</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -4078,22 +3991,22 @@
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A39" s="2" t="s">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="B39" t="s">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="C39" t="s">
-        <v>142</v>
+        <v>112</v>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F39" t="s">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -4128,22 +4041,22 @@
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A40" s="2" t="s">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="B40" t="s">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="C40" t="s">
-        <v>144</v>
+        <v>113</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F40" t="s">
-        <v>145</v>
+        <v>104</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -4178,13 +4091,13 @@
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A41" s="2" t="s">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="B41" t="s">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="C41" t="s">
-        <v>146</v>
+        <v>101</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -4193,7 +4106,7 @@
         <v>1</v>
       </c>
       <c r="F41" t="s">
-        <v>147</v>
+        <v>102</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -4228,13 +4141,13 @@
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A42" s="2" t="s">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="B42" t="s">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="C42" t="s">
-        <v>148</v>
+        <v>105</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -4243,7 +4156,7 @@
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>149</v>
+        <v>106</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -4278,28 +4191,31 @@
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A43" s="2" t="s">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="B43" t="s">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="C43" t="s">
-        <v>150</v>
+        <v>107</v>
       </c>
       <c r="D43">
         <v>1</v>
       </c>
       <c r="E43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F43" t="s">
-        <v>151</v>
+        <v>108</v>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I43" t="s">
+        <v>109</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -4328,13 +4244,13 @@
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A44" s="2" t="s">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="B44" t="s">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="C44" t="s">
-        <v>152</v>
+        <v>110</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -4343,13 +4259,16 @@
         <v>1</v>
       </c>
       <c r="F44" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I44" t="s">
+        <v>98</v>
       </c>
       <c r="J44">
         <v>0</v>
@@ -4378,22 +4297,22 @@
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A45" s="2" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="B45" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="C45" t="s">
-        <v>153</v>
+        <v>128</v>
       </c>
       <c r="D45">
         <v>1</v>
       </c>
       <c r="E45">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F45" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -4428,22 +4347,22 @@
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A46" s="2" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="B46" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="C46" t="s">
-        <v>172</v>
+        <v>127</v>
       </c>
       <c r="D46">
         <v>1</v>
       </c>
       <c r="E46">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F46" t="s">
-        <v>173</v>
+        <v>60</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -4478,22 +4397,22 @@
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A47" s="2" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="B47" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="C47" t="s">
-        <v>174</v>
+        <v>141</v>
       </c>
       <c r="D47">
         <v>1</v>
       </c>
       <c r="E47">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F47" t="s">
-        <v>175</v>
+        <v>142</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -4528,72 +4447,72 @@
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A48" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B48" t="s">
+        <v>126</v>
+      </c>
+      <c r="C48" t="s">
+        <v>137</v>
+      </c>
+      <c r="D48">
+        <v>1</v>
+      </c>
+      <c r="E48">
+        <v>1</v>
+      </c>
+      <c r="F48" t="s">
         <v>138</v>
       </c>
-      <c r="B48" t="s">
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>0</v>
+      </c>
+      <c r="S48">
+        <v>0</v>
+      </c>
+      <c r="T48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.15">
+      <c r="A49" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B49" t="s">
+        <v>126</v>
+      </c>
+      <c r="C49" t="s">
         <v>139</v>
       </c>
-      <c r="C48" t="s">
-        <v>176</v>
-      </c>
-      <c r="D48">
-        <v>1</v>
-      </c>
-      <c r="E48">
-        <v>1</v>
-      </c>
-      <c r="F48" t="s">
-        <v>177</v>
-      </c>
-      <c r="G48">
-        <v>0</v>
-      </c>
-      <c r="H48">
-        <v>0</v>
-      </c>
-      <c r="J48">
-        <v>0</v>
-      </c>
-      <c r="K48">
-        <v>0</v>
-      </c>
-      <c r="M48">
-        <v>0</v>
-      </c>
-      <c r="N48">
-        <v>0</v>
-      </c>
-      <c r="P48">
-        <v>0</v>
-      </c>
-      <c r="Q48">
-        <v>0</v>
-      </c>
-      <c r="S48">
-        <v>0</v>
-      </c>
-      <c r="T48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A49" s="2">
-        <v>3</v>
-      </c>
-      <c r="B49" t="s">
-        <v>37</v>
-      </c>
-      <c r="C49" t="s">
-        <v>38</v>
-      </c>
       <c r="D49">
         <v>1</v>
       </c>
       <c r="E49">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F49" t="s">
-        <v>39</v>
+        <v>140</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -4628,22 +4547,22 @@
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A50" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B50" t="s">
+        <v>126</v>
+      </c>
+      <c r="C50" t="s">
         <v>132</v>
       </c>
-      <c r="B50" t="s">
-        <v>37</v>
-      </c>
-      <c r="C50" t="s">
+      <c r="D50">
+        <v>1</v>
+      </c>
+      <c r="E50">
+        <v>1</v>
+      </c>
+      <c r="F50" t="s">
         <v>133</v>
-      </c>
-      <c r="D50">
-        <v>1</v>
-      </c>
-      <c r="E50">
-        <v>1</v>
-      </c>
-      <c r="F50" t="s">
-        <v>134</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -4678,22 +4597,22 @@
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A51" s="2" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="B51" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="C51" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D51">
         <v>1</v>
       </c>
       <c r="E51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F51" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -4728,13 +4647,13 @@
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A52" s="2" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="B52" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="C52" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -4743,7 +4662,7 @@
         <v>1</v>
       </c>
       <c r="F52" t="s">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -4778,22 +4697,22 @@
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.15">
       <c r="A53" s="2" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="B53" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="C53" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D53">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E53">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="F53" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -4823,718 +4742,12 @@
         <v>0</v>
       </c>
       <c r="T53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A54" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B54" t="s">
-        <v>116</v>
-      </c>
-      <c r="C54" t="s">
-        <v>123</v>
-      </c>
-      <c r="D54">
-        <v>1</v>
-      </c>
-      <c r="E54">
-        <v>1</v>
-      </c>
-      <c r="F54" t="s">
-        <v>124</v>
-      </c>
-      <c r="G54">
-        <v>0</v>
-      </c>
-      <c r="H54">
-        <v>0</v>
-      </c>
-      <c r="J54">
-        <v>0</v>
-      </c>
-      <c r="K54">
-        <v>0</v>
-      </c>
-      <c r="M54">
-        <v>0</v>
-      </c>
-      <c r="N54">
-        <v>0</v>
-      </c>
-      <c r="P54">
-        <v>0</v>
-      </c>
-      <c r="Q54">
-        <v>0</v>
-      </c>
-      <c r="S54">
-        <v>0</v>
-      </c>
-      <c r="T54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A55" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B55" t="s">
-        <v>116</v>
-      </c>
-      <c r="C55" t="s">
-        <v>125</v>
-      </c>
-      <c r="D55">
-        <v>1</v>
-      </c>
-      <c r="E55">
-        <v>1</v>
-      </c>
-      <c r="F55" t="s">
-        <v>126</v>
-      </c>
-      <c r="G55">
-        <v>1</v>
-      </c>
-      <c r="H55">
-        <v>1</v>
-      </c>
-      <c r="I55" t="s">
-        <v>127</v>
-      </c>
-      <c r="J55">
-        <v>0</v>
-      </c>
-      <c r="K55">
-        <v>0</v>
-      </c>
-      <c r="M55">
-        <v>0</v>
-      </c>
-      <c r="N55">
-        <v>0</v>
-      </c>
-      <c r="P55">
-        <v>0</v>
-      </c>
-      <c r="Q55">
-        <v>0</v>
-      </c>
-      <c r="S55">
-        <v>0</v>
-      </c>
-      <c r="T55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A56" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B56" t="s">
-        <v>116</v>
-      </c>
-      <c r="C56" t="s">
-        <v>128</v>
-      </c>
-      <c r="D56">
-        <v>1</v>
-      </c>
-      <c r="E56">
-        <v>1</v>
-      </c>
-      <c r="F56" t="s">
-        <v>129</v>
-      </c>
-      <c r="G56">
-        <v>1</v>
-      </c>
-      <c r="H56">
-        <v>1</v>
-      </c>
-      <c r="I56" t="s">
-        <v>114</v>
-      </c>
-      <c r="J56">
-        <v>0</v>
-      </c>
-      <c r="K56">
-        <v>0</v>
-      </c>
-      <c r="M56">
-        <v>0</v>
-      </c>
-      <c r="N56">
-        <v>0</v>
-      </c>
-      <c r="P56">
-        <v>0</v>
-      </c>
-      <c r="Q56">
-        <v>0</v>
-      </c>
-      <c r="S56">
-        <v>0</v>
-      </c>
-      <c r="T56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A57" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B57" t="s">
-        <v>116</v>
-      </c>
-      <c r="C57" t="s">
-        <v>130</v>
-      </c>
-      <c r="D57">
-        <v>16</v>
-      </c>
-      <c r="E57">
-        <v>100</v>
-      </c>
-      <c r="F57" t="s">
-        <v>122</v>
-      </c>
-      <c r="G57">
-        <v>0</v>
-      </c>
-      <c r="H57">
-        <v>0</v>
-      </c>
-      <c r="J57">
-        <v>0</v>
-      </c>
-      <c r="K57">
-        <v>0</v>
-      </c>
-      <c r="M57">
-        <v>0</v>
-      </c>
-      <c r="N57">
-        <v>0</v>
-      </c>
-      <c r="P57">
-        <v>0</v>
-      </c>
-      <c r="Q57">
-        <v>0</v>
-      </c>
-      <c r="S57">
-        <v>0</v>
-      </c>
-      <c r="T57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A58" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B58" t="s">
-        <v>116</v>
-      </c>
-      <c r="C58" t="s">
-        <v>131</v>
-      </c>
-      <c r="D58">
-        <v>22</v>
-      </c>
-      <c r="E58">
-        <v>100</v>
-      </c>
-      <c r="F58" t="s">
-        <v>122</v>
-      </c>
-      <c r="G58">
-        <v>0</v>
-      </c>
-      <c r="H58">
-        <v>0</v>
-      </c>
-      <c r="J58">
-        <v>0</v>
-      </c>
-      <c r="K58">
-        <v>0</v>
-      </c>
-      <c r="M58">
-        <v>0</v>
-      </c>
-      <c r="N58">
-        <v>0</v>
-      </c>
-      <c r="P58">
-        <v>0</v>
-      </c>
-      <c r="Q58">
-        <v>0</v>
-      </c>
-      <c r="S58">
-        <v>0</v>
-      </c>
-      <c r="T58">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A59" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="B59" t="s">
-        <v>155</v>
-      </c>
-      <c r="C59" t="s">
-        <v>156</v>
-      </c>
-      <c r="D59">
-        <v>1</v>
-      </c>
-      <c r="E59">
-        <v>4</v>
-      </c>
-      <c r="F59" t="s">
-        <v>72</v>
-      </c>
-      <c r="G59">
-        <v>0</v>
-      </c>
-      <c r="H59">
-        <v>0</v>
-      </c>
-      <c r="J59">
-        <v>0</v>
-      </c>
-      <c r="K59">
-        <v>0</v>
-      </c>
-      <c r="M59">
-        <v>0</v>
-      </c>
-      <c r="N59">
-        <v>0</v>
-      </c>
-      <c r="P59">
-        <v>0</v>
-      </c>
-      <c r="Q59">
-        <v>0</v>
-      </c>
-      <c r="S59">
-        <v>0</v>
-      </c>
-      <c r="T59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A60" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="B60" t="s">
-        <v>155</v>
-      </c>
-      <c r="C60" t="s">
-        <v>157</v>
-      </c>
-      <c r="D60">
-        <v>1</v>
-      </c>
-      <c r="E60">
-        <v>8</v>
-      </c>
-      <c r="F60" t="s">
-        <v>158</v>
-      </c>
-      <c r="G60">
-        <v>0</v>
-      </c>
-      <c r="H60">
-        <v>0</v>
-      </c>
-      <c r="J60">
-        <v>0</v>
-      </c>
-      <c r="K60">
-        <v>0</v>
-      </c>
-      <c r="M60">
-        <v>0</v>
-      </c>
-      <c r="N60">
-        <v>0</v>
-      </c>
-      <c r="P60">
-        <v>0</v>
-      </c>
-      <c r="Q60">
-        <v>0</v>
-      </c>
-      <c r="S60">
-        <v>0</v>
-      </c>
-      <c r="T60">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A61" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="B61" t="s">
-        <v>155</v>
-      </c>
-      <c r="C61" t="s">
-        <v>159</v>
-      </c>
-      <c r="D61">
-        <v>1</v>
-      </c>
-      <c r="E61">
-        <v>3</v>
-      </c>
-      <c r="F61" t="s">
-        <v>160</v>
-      </c>
-      <c r="G61">
-        <v>0</v>
-      </c>
-      <c r="H61">
-        <v>0</v>
-      </c>
-      <c r="J61">
-        <v>0</v>
-      </c>
-      <c r="K61">
-        <v>0</v>
-      </c>
-      <c r="M61">
-        <v>0</v>
-      </c>
-      <c r="N61">
-        <v>0</v>
-      </c>
-      <c r="P61">
-        <v>0</v>
-      </c>
-      <c r="Q61">
-        <v>0</v>
-      </c>
-      <c r="S61">
-        <v>0</v>
-      </c>
-      <c r="T61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A62" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="B62" t="s">
-        <v>155</v>
-      </c>
-      <c r="C62" t="s">
-        <v>161</v>
-      </c>
-      <c r="D62">
-        <v>1</v>
-      </c>
-      <c r="E62">
-        <v>1</v>
-      </c>
-      <c r="F62" t="s">
-        <v>162</v>
-      </c>
-      <c r="G62">
-        <v>0</v>
-      </c>
-      <c r="H62">
-        <v>0</v>
-      </c>
-      <c r="J62">
-        <v>0</v>
-      </c>
-      <c r="K62">
-        <v>0</v>
-      </c>
-      <c r="M62">
-        <v>0</v>
-      </c>
-      <c r="N62">
-        <v>0</v>
-      </c>
-      <c r="P62">
-        <v>0</v>
-      </c>
-      <c r="Q62">
-        <v>0</v>
-      </c>
-      <c r="S62">
-        <v>0</v>
-      </c>
-      <c r="T62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A63" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="B63" t="s">
-        <v>155</v>
-      </c>
-      <c r="C63" t="s">
-        <v>163</v>
-      </c>
-      <c r="D63">
-        <v>1</v>
-      </c>
-      <c r="E63">
-        <v>4</v>
-      </c>
-      <c r="F63" t="s">
-        <v>164</v>
-      </c>
-      <c r="G63">
-        <v>0</v>
-      </c>
-      <c r="H63">
-        <v>0</v>
-      </c>
-      <c r="J63">
-        <v>0</v>
-      </c>
-      <c r="K63">
-        <v>0</v>
-      </c>
-      <c r="M63">
-        <v>0</v>
-      </c>
-      <c r="N63">
-        <v>0</v>
-      </c>
-      <c r="P63">
-        <v>0</v>
-      </c>
-      <c r="Q63">
-        <v>0</v>
-      </c>
-      <c r="S63">
-        <v>0</v>
-      </c>
-      <c r="T63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A64" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="B64" t="s">
-        <v>155</v>
-      </c>
-      <c r="C64" t="s">
-        <v>165</v>
-      </c>
-      <c r="D64">
-        <v>1</v>
-      </c>
-      <c r="E64">
-        <v>1</v>
-      </c>
-      <c r="F64" t="s">
-        <v>72</v>
-      </c>
-      <c r="G64">
-        <v>0</v>
-      </c>
-      <c r="H64">
-        <v>0</v>
-      </c>
-      <c r="J64">
-        <v>0</v>
-      </c>
-      <c r="K64">
-        <v>0</v>
-      </c>
-      <c r="M64">
-        <v>0</v>
-      </c>
-      <c r="N64">
-        <v>0</v>
-      </c>
-      <c r="P64">
-        <v>0</v>
-      </c>
-      <c r="Q64">
-        <v>0</v>
-      </c>
-      <c r="S64">
-        <v>0</v>
-      </c>
-      <c r="T64">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A65" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="B65" t="s">
-        <v>155</v>
-      </c>
-      <c r="C65" t="s">
-        <v>166</v>
-      </c>
-      <c r="D65">
-        <v>1</v>
-      </c>
-      <c r="E65">
-        <v>1</v>
-      </c>
-      <c r="F65" t="s">
-        <v>167</v>
-      </c>
-      <c r="G65">
-        <v>0</v>
-      </c>
-      <c r="H65">
-        <v>0</v>
-      </c>
-      <c r="J65">
-        <v>0</v>
-      </c>
-      <c r="K65">
-        <v>0</v>
-      </c>
-      <c r="M65">
-        <v>0</v>
-      </c>
-      <c r="N65">
-        <v>0</v>
-      </c>
-      <c r="P65">
-        <v>0</v>
-      </c>
-      <c r="Q65">
-        <v>0</v>
-      </c>
-      <c r="S65">
-        <v>0</v>
-      </c>
-      <c r="T65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A66" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="B66" t="s">
-        <v>155</v>
-      </c>
-      <c r="C66" t="s">
-        <v>168</v>
-      </c>
-      <c r="D66">
-        <v>1</v>
-      </c>
-      <c r="E66">
-        <v>4</v>
-      </c>
-      <c r="F66" t="s">
-        <v>169</v>
-      </c>
-      <c r="G66">
-        <v>0</v>
-      </c>
-      <c r="H66">
-        <v>0</v>
-      </c>
-      <c r="J66">
-        <v>0</v>
-      </c>
-      <c r="K66">
-        <v>0</v>
-      </c>
-      <c r="M66">
-        <v>0</v>
-      </c>
-      <c r="N66">
-        <v>0</v>
-      </c>
-      <c r="P66">
-        <v>0</v>
-      </c>
-      <c r="Q66">
-        <v>0</v>
-      </c>
-      <c r="S66">
-        <v>0</v>
-      </c>
-      <c r="T66">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A67" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="B67" t="s">
-        <v>155</v>
-      </c>
-      <c r="C67" t="s">
-        <v>170</v>
-      </c>
-      <c r="D67">
-        <v>1</v>
-      </c>
-      <c r="E67">
-        <v>7</v>
-      </c>
-      <c r="F67" t="s">
-        <v>171</v>
-      </c>
-      <c r="G67">
-        <v>0</v>
-      </c>
-      <c r="H67">
-        <v>0</v>
-      </c>
-      <c r="J67">
-        <v>0</v>
-      </c>
-      <c r="K67">
-        <v>0</v>
-      </c>
-      <c r="M67">
-        <v>0</v>
-      </c>
-      <c r="N67">
-        <v>0</v>
-      </c>
-      <c r="P67">
-        <v>0</v>
-      </c>
-      <c r="Q67">
-        <v>0</v>
-      </c>
-      <c r="S67">
-        <v>0</v>
-      </c>
-      <c r="T67">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:U1">
-    <sortState ref="A2:U67">
+    <sortState ref="A2:U53">
       <sortCondition ref="B1"/>
     </sortState>
   </autoFilter>
@@ -5592,13 +4805,13 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A2" s="6" t="s">
-        <v>178</v>
+        <v>149</v>
       </c>
       <c r="B2" t="s">
-        <v>179</v>
+        <v>150</v>
       </c>
       <c r="C2" t="s">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -5607,7 +4820,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>181</v>
+        <v>152</v>
       </c>
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
@@ -5625,13 +4838,13 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A5" s="6" t="s">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="B5" t="s">
-        <v>179</v>
+        <v>150</v>
       </c>
       <c r="C5" t="s">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -5640,7 +4853,7 @@
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>181</v>
+        <v>152</v>
       </c>
       <c r="G5" s="7">
         <v>1</v>
@@ -5649,7 +4862,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>183</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.15">
@@ -5669,13 +4882,13 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A9" s="6" t="s">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="B9" t="s">
-        <v>179</v>
+        <v>150</v>
       </c>
       <c r="C9" t="s">
-        <v>184</v>
+        <v>155</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -5684,7 +4897,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>181</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.15">
@@ -5699,13 +4912,13 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A12" s="6" t="s">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s">
-        <v>179</v>
+        <v>150</v>
       </c>
       <c r="C12" t="s">
-        <v>184</v>
+        <v>155</v>
       </c>
       <c r="D12" s="7">
         <v>1</v>
@@ -5714,7 +4927,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>185</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.15">
@@ -5729,13 +4942,13 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A16" s="6" t="s">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="B16" t="s">
-        <v>179</v>
+        <v>150</v>
       </c>
       <c r="C16" t="s">
-        <v>184</v>
+        <v>155</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -5744,7 +4957,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>181</v>
+        <v>152</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.15">
@@ -5759,13 +4972,13 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A19" s="6" t="s">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="B19" t="s">
-        <v>179</v>
+        <v>150</v>
       </c>
       <c r="C19" t="s">
-        <v>184</v>
+        <v>155</v>
       </c>
       <c r="D19" s="7">
         <v>1</v>
@@ -5774,7 +4987,7 @@
         <v>1</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>181</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.15">
@@ -5794,13 +5007,13 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A23" s="6" t="s">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="B23" t="s">
-        <v>179</v>
+        <v>150</v>
       </c>
       <c r="C23" t="s">
-        <v>186</v>
+        <v>157</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -5809,18 +5022,18 @@
         <v>1</v>
       </c>
       <c r="F23" t="s">
-        <v>181</v>
+        <v>152</v>
       </c>
     </row>
     <row r="26" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A26" s="10" t="s">
-        <v>178</v>
+        <v>149</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>179</v>
+        <v>150</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>187</v>
+        <v>158</v>
       </c>
       <c r="D26" s="11">
         <v>1</v>
@@ -5829,7 +5042,7 @@
         <v>1</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>188</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
